--- a/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable. Papa dit : on mange ensemble, à table. Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
+          <t>Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable. On mange ensemble, à table. Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable.
+papa|On mange ensemble, à table.
+narrateur|Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo va manger. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Kenzo boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,11 @@
 narrateur|Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1505,7 @@
           <t>narrateur|Kenzo va manger. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1677,7 @@
           <t>narrateur|Kenzo est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1845,7 @@
           <t>narrateur|Kenzo boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kenzo s'assoit au jardin</t>
+          <t>La nappe à carreaux</t>
         </is>
       </c>
     </row>
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.001</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -830,6 +835,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Les ombres des feuilles bougent. Papa pose une nappe à carreaux. Victorino amène sa chaise. On mange assis, au jardin. Il croque une tomate.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable. On mange ensemble, à table. Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
+          <t>Les feuilles dansent sur l'herbe. Leurs ombres bougent, tout doucement. Une abeille va de fleur en fleur. Elle fait un petit bourdon. La table du jardin est encore tiède. Victorino vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent encore le soleil. Une pierre tiède sert de marche. Papa déplie une nappe. La nappe a des carreaux rouges. On dirait un damier ! Oui. Un damier pour manger. Tu m'aides à la poser ? Oui, papa. Ils tirent la nappe ensemble. Le vent la soulève un peu. J'apporte le panier ! Le panier sent le pain. Maman le pose au milieu. Victorino, c'est l'heure. Viens t'asseoir. Victorino va vers sa chaise. L'herbe chatouille ses chevilles. Il tire la chaise. Il s'assoit à table. Il pose les pieds par terre. Bravo, Victorino. Tu es bien assis. Papa s'assoit aussi. Maman s'assoit près de lui. On est ensemble. On mange à table. La chaise ne bouge plus. Tu poses les mains sur la nappe ? Victorino pose les mains. Les carreaux sont un peu rudes. Tu as entendu l'abeille ? Elle bourdonne. Une tomate rouge attend dans l'assiette. Elle est lisse et tiède. Tu as vu comme elle brille ? Oui. Comme un ballon. On attend un petit moment. Le repas est calme, parce qu'on est assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1329,57 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est assis à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable.
-papa|On mange ensemble, à table.
-narrateur|Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.</t>
+          <t>narrateur|Les feuilles dansent sur l'herbe.
+narrateur|Leurs ombres bougent, tout doucement.
+narrateur|Une abeille va de fleur en fleur.
+narrateur|Elle fait un petit bourdon.
+narrateur|La table du jardin est encore tiède.
+narrateur|Victorino vit ici, avec papa et maman.
+narrateur|La maison est juste derrière.
+narrateur|L'herbe sent encore le soleil.
+narrateur|Une pierre tiède sert de marche.
+narrateur|Papa déplie une nappe.
+narrateur|La nappe a des carreaux rouges.
+enfant-m|On dirait un damier !
+papa|Oui. Un damier pour manger.
+papa|Tu m'aides à la poser ?
+enfant-m|Oui, papa.
+narrateur|Ils tirent la nappe ensemble.
+narrateur|Le vent la soulève un peu.
+maman|J'apporte le panier !
+narrateur|Le panier sent le pain.
+narrateur|Maman le pose au milieu.
+maman|Victorino, c'est l'heure.
+maman|Viens t'asseoir.
+narrateur|Victorino va vers sa chaise.
+narrateur|L'herbe chatouille ses chevilles.
+narrateur|Il tire la chaise.
+narrateur|Il s'assoit à table.
+narrateur|Il pose les pieds par terre.
+papa|Bravo, Victorino.
+papa|Tu es bien assis.
+narrateur|Papa s'assoit aussi.
+narrateur|Maman s'assoit près de lui.
+maman|On est ensemble.
+maman|On mange à table.
+narrateur|La chaise ne bouge plus.
+papa|Tu poses les mains sur la nappe ?
+narrateur|Victorino pose les mains.
+narrateur|Les carreaux sont un peu rudes.
+maman|Tu as entendu l'abeille ?
+enfant-m|Elle bourdonne.
+narrateur|Une tomate rouge attend dans l'assiette.
+narrateur|Elle est lisse et tiède.
+maman|Tu as vu comme elle brille ?
+enfant-m|Oui.
+enfant-m|Comme un ballon.
+papa|On attend un petit moment.
+narrateur|Le repas est calme, parce qu'on est assis.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>nappe,chaise</t>
         </is>
       </c>
     </row>
@@ -1346,7 +1406,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Kenzo va manger. Que fait-il ?</t>
+          <t>Victorino va manger. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo va manger. Que fait-il ?</t>
+          <t>narrateur|Victorino va manger.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Kenzo est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>Victorino est assis. Il est à table. On est tous assis. On est ensemble. Le pain attend. Ta chaise reste à table ? Oui. Victorino reste assis. Une feuille tombe sur la nappe. Tu la laisses là ? Oui. Elle est jolie. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1735,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo est assis. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.</t>
+          <t>narrateur|Victorino est assis.
+narrateur|Il est à table.
+papa|On est tous assis.
+maman|On est ensemble.
+narrateur|Le pain attend.
+papa|Ta chaise reste à table ?
+enfant-m|Oui.
+narrateur|Victorino reste assis.
+narrateur|Une feuille tombe sur la nappe.
+papa|Tu la laisses là ?
+enfant-m|Oui.
+enfant-m|Elle est jolie.
+maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1775,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Kenzo boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+          <t>La tomate est là. Tu prends ta fourchette ? Victorino prend sa fourchette. Tu restes assis. Il croque un petit morceau. C'est juteux. C'est bon. Bravo, Victorino. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Victorino. Ils mangent ensemble. Victorino reste assis. Encore une petite bouchée ? Encore une bouchée. La nappe ne bouge plus. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Victorino. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1915,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Kenzo boit une gorgée. Il reste assis jusqu'à la fin. Merci, dit papa.</t>
+          <t>narrateur|La tomate est là.
+maman|Tu prends ta fourchette ?
+narrateur|Victorino prend sa fourchette.
+papa|Tu restes assis.
+narrateur|Il croque un petit morceau.
+enfant-m|C'est juteux.
+enfant-m|C'est bon.
+maman|Bravo, Victorino.
+maman|Tu as goûté.
+maman|C'est du bon travail.
+papa|Bon appétit.
+maman|Bon appétit, Victorino.
+narrateur|Ils mangent ensemble.
+narrateur|Victorino reste assis.
+papa|Encore une petite bouchée ?
+narrateur|Encore une bouchée.
+narrateur|La nappe ne bouge plus.
+papa|Tu restes assis. Bravo.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.
+maman|Merci, Victorino.
+narrateur|Il boit une gorgée.
+narrateur|Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>L'abeille s'en va. La nappe reste sur la table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2105,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|L'abeille s'en va.
+narrateur|La nappe reste sur la table.
+papa|On a mangé assis, ensemble.
+enfant-m|C'était bon.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les feuilles dansent sur l'herbe. Leurs ombres bougent, tout doucement. Une abeille va de fleur en fleur. Elle fait un petit bourdon. La table du jardin est encore tiède. Victorino vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent encore le soleil. Une pierre tiède sert de marche. Papa déplie une nappe. La nappe a des carreaux rouges. On dirait un damier ! Oui. Un damier pour manger. Tu m'aides à la poser ? Oui, papa. Ils tirent la nappe ensemble. Le vent la soulève un peu. J'apporte le panier ! Le panier sent le pain. Maman le pose au milieu. Victorino, c'est l'heure. Viens t'asseoir. Victorino va vers sa chaise. L'herbe chatouille ses chevilles. Il tire la chaise. Il s'assoit à table. Il pose les pieds par terre. Bravo, Victorino. Tu es bien assis. Papa s'assoit aussi. Maman s'assoit près de lui. On est ensemble. On mange à table. La chaise ne bouge plus. Tu poses les mains sur la nappe ? Victorino pose les mains. Les carreaux sont un peu rudes. Tu as entendu l'abeille ? Elle bourdonne. Une tomate rouge attend dans l'assiette. Elle est lisse et tiède. Tu as vu comme elle brille ? Oui. Comme un ballon. On attend un petit moment. Le repas est calme, parce qu'on est assis.</t>
+          <t>Les feuilles dansent sur l'herbe. Leurs ombres bougent, tout doucement. Une abeille va de fleur en fleur. Elle fait un petit bourdon. La table du jardin est encore tiède. Victorino vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent encore le soleil. Une pierre tiède sert de marche. Papa déplie une nappe. La nappe a des carreaux rouges. On dirait un damier ! Oui. Un damier pour manger. Tu m'aides à la poser ? Oui, papa. Ils tirent la nappe ensemble. Le vent la soulève un peu. J'apporte le panier ! Le panier sent le pain. Maman le pose au milieu. Victorino, c'est l'heure. Viens t'asseoir. Victorino va vers sa chaise. L'herbe chatouille ses chevilles. Il tire la chaise. Il s'assoit à table. Il pose les pieds par terre. Bravo, Victorino. Tu es bien assis. Papa s'assoit aussi. Maman s'assoit près de Victorino. On est ensemble. On mange à table. La chaise ne bouge plus. Tu poses les mains sur la nappe ? Victorino pose les mains. Les carreaux sont un peu rudes. Tu as entendu l'abeille ? Elle bourdonne. Une tomate rouge attend dans l'assiette. Elle est lisse et tiède. Tu as vu comme elle brille ? Oui. Comme un ballon. On attend un petit moment. Le repas est calme, parce qu'on est assis.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo joue dans le jardin. Les abeilles bourdonnent. Papa pose une nappe sur la table. Maman apporte le panier. Ça sent le pain. C'est l'heure de manger. Kenzo a faim. Parce qu'on mange ensemble, Kenzo va s'asseoir. Il pose les fesses sur la chaise. Il est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; à table. Papa s'assoit aussi. Maman s'assoit près de Kenzo. Ils sont ensemble. Kenzo tient sa fourchette. Il mange assis. La chaise est stable. Papa dit : on mange ensemble, à table. Kenzo sourit. Il reste assis. Il croque une tomate. Elle est juteuse. Maman coupe le pain. Kenzo attend, assis. Parce qu'il est assis, le repas est calme.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les feuilles dansent sur l'herbe. Leurs ombres bougent, tout doucement. Une abeille va de fleur en fleur. Elle fait un petit bourdon. La table du jardin est encore tiède. Victorino vit ici, avec papa et maman. La maison est juste derrière. L'herbe sent encore le soleil. Une pierre tiède sert de marche. Papa déplie une nappe. La nappe a des carreaux rouges. On dirait un damier ! Oui. Un damier pour manger. Tu m'aides à la poser ? Oui, papa. Ils tirent la nappe ensemble. Le vent la soulève un peu. J'apporte le panier ! Le panier sent le pain. Maman le pose au milieu. Victorino, c'est l'heure. Viens t'asseoir. Victorino va vers sa chaise. L'herbe chatouille ses chevilles. Il tire la chaise. Il s'assoit à table. Il pose les pieds par terre. Bravo, Victorino. Tu es bien assis. Papa s'assoit aussi. Maman s'assoit près de Victorino. On est ensemble. On mange à table. La chaise ne bouge plus. Tu poses les mains sur la nappe ? Victorino pose les mains. Les carreaux sont un peu rudes. Tu as entendu l'abeille ? Elle bourdonne. Une tomate rouge attend dans l'assiette. Elle est lisse et tiède. Tu as vu comme elle brille ? Oui. Comme un ballon. On attend un petit moment. Le repas est calme, parce qu'on est assis.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,7 @@
 papa|Bravo, Victorino.
 papa|Tu es bien assis.
 narrateur|Papa s'assoit aussi.
-narrateur|Maman s'assoit près de lui.
+narrateur|Maman s'assoit près de Victorino.
 maman|On est ensemble.
 maman|On mange à table.
 narrateur|La chaise ne bouge plus.
@@ -1411,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Kenzo va manger. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino va manger. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1566,7 +1566,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,7 +1595,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo est &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;. Les fesses sont sur la chaise. Papa et maman mangent ensemble, à table.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino est assis. Il est à table. On est tous assis. On est ensemble. Le pain attend. Ta chaise reste à table ? Oui. Victorino reste assis. Une feuille tombe sur la nappe. Tu la laisses là ? Oui. Elle est jolie. Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1750,7 +1749,6 @@
 maman|Bravo. Tu attends un petit moment.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1775,12 +1773,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>La tomate est là. Tu prends ta fourchette ? Victorino prend sa fourchette. Tu restes assis. Il croque un petit morceau. C'est juteux. C'est bon. Bravo, Victorino. Tu as goûté. C'est du bon travail. Bon appétit. Bon appétit, Victorino. Ils mangent ensemble. Victorino reste assis. Encore une petite bouchée ? Encore une bouchée. La nappe ne bouge plus. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Victorino. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
+          <t>La tomate est là. Tu prends ta fourchette ? Victorino prend sa fourchette. Tu restes assis. Il croque un petit morceau. C'est juteux. C'est bon. Bravo, Victorino. Tu as goûté. Bon appétit. Bon appétit, Victorino. Ils mangent ensemble. Victorino reste assis. Encore une petite bouchée ? Encore une bouchée. La nappe ne bouge plus. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Victorino. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Kenzo boit une gorgée. Il reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt; jusqu'à la fin. Merci, dit papa.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>La tomate est là. Tu prends ta fourchette ? Victorino prend sa fourchette. Tu restes assis. Il croque un petit morceau. C'est juteux. C'est bon. Bravo, Victorino. Tu as goûté. Bon appétit. Bon appétit, Victorino. Ils mangent ensemble. Victorino reste assis. Encore une petite bouchée ? Encore une bouchée. La nappe ne bouge plus. Tu restes assis. Bravo. Merci, maman. Merci, papa. Merci, Victorino. Il boit une gorgée. Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1924,7 +1922,6 @@
 enfant-m|C'est bon.
 maman|Bravo, Victorino.
 maman|Tu as goûté.
-maman|C'est du bon travail.
 papa|Bon appétit.
 maman|Bon appétit, Victorino.
 narrateur|Ils mangent ensemble.
@@ -1940,7 +1937,6 @@
 narrateur|Il reste assis jusqu'à la fin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'abeille s'en va. La nappe reste sur la table. On a mangé assis, ensemble. C'était bon. Bravo. Tu as fait du bon travail. L'histoire est finie.</t>
+          <t>L'abeille s'en va. La nappe reste sur la table. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>L'abeille s'en va. La nappe reste sur la table. On a mangé assis, ensemble. C'était bon. Bravo.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2105,9 @@
 narrateur|La nappe reste sur la table.
 papa|On a mangé assis, ensemble.
 enfant-m|C'était bon.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Bravo.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2171,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.002-02.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Kenzo, papa, maman</t>
+          <t>Victorino, papa, maman</t>
         </is>
       </c>
     </row>
